--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_MACCABI RAPYD TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_MACCABI RAPYD TEL AVIV.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>60.0098</v>
+        <v>43.9234</v>
       </c>
       <c r="E2" t="n">
-        <v>55.7397</v>
+        <v>42.2259</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2698</v>
+        <v>1.6968</v>
       </c>
       <c r="G2" t="n">
         <v>13.8488</v>
@@ -610,13 +610,13 @@
         <v>35.7209</v>
       </c>
       <c r="S2" t="n">
-        <v>20.1106</v>
+        <v>4.0236</v>
       </c>
       <c r="T2" t="n">
-        <v>21.2092</v>
+        <v>7.696</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0989</v>
+        <v>-3.6719</v>
       </c>
       <c r="V2" t="n">
         <v>4.479200000000001</v>
@@ -643,13 +643,13 @@
         <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>41.9433</v>
+        <v>21.125</v>
       </c>
       <c r="E3" t="n">
-        <v>45.1736</v>
+        <v>31.9978</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.230299999999999</v>
+        <v>-10.8724</v>
       </c>
       <c r="G3" t="n">
         <v>-39.2713</v>
@@ -688,13 +688,13 @@
         <v>70.9776</v>
       </c>
       <c r="S3" t="n">
-        <v>32.4461</v>
+        <v>11.6283</v>
       </c>
       <c r="T3" t="n">
-        <v>21.6934</v>
+        <v>8.5175</v>
       </c>
       <c r="U3" t="n">
-        <v>10.7534</v>
+        <v>3.1107</v>
       </c>
       <c r="V3" t="n">
         <v>24.6455</v>
@@ -721,13 +721,13 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>10.0347</v>
+        <v>17.4059</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9602</v>
+        <v>15.6741</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9253999999999996</v>
+        <v>1.7322</v>
       </c>
       <c r="G4" t="n">
         <v>-5.622699999999999</v>
@@ -766,13 +766,13 @@
         <v>32.2414</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1357</v>
+        <v>8.507</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5117</v>
+        <v>8.2254</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.3761</v>
+        <v>0.2814000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-6.3536</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9.9473</v>
+        <v>7.7323</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2101</v>
+        <v>10.3673</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.262899999999999</v>
+        <v>-2.6349</v>
       </c>
       <c r="G5" t="n">
         <v>8.7317</v>
@@ -844,13 +844,13 @@
         <v>7.4227</v>
       </c>
       <c r="S5" t="n">
-        <v>8.2598</v>
+        <v>6.0449</v>
       </c>
       <c r="T5" t="n">
-        <v>7.3813</v>
+        <v>4.5384</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8786</v>
+        <v>1.5064</v>
       </c>
       <c r="V5" t="n">
         <v>-8.4358</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>7.162699999999999</v>
+        <v>7.155999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9884</v>
+        <v>7.089700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.825699999999999</v>
+        <v>0.06630000000000047</v>
       </c>
       <c r="G6" t="n">
-        <v>-25.6569</v>
+        <v>3.857199999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.3575</v>
+        <v>1.3214</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.2995</v>
+        <v>2.5357</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3386</v>
+        <v>23.574</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.5076</v>
+        <v>12.9569</v>
       </c>
       <c r="L6" t="n">
-        <v>4.846399999999999</v>
+        <v>10.617</v>
       </c>
       <c r="M6" t="n">
-        <v>-25.9956</v>
+        <v>-19.7171</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.8499</v>
+        <v>-11.6354</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.1459</v>
+        <v>-8.0815</v>
       </c>
       <c r="P6" t="n">
-        <v>26.6747</v>
+        <v>-5.7989</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.278499999999999</v>
+        <v>-33.633</v>
       </c>
       <c r="R6" t="n">
-        <v>35.953</v>
+        <v>27.8344</v>
       </c>
       <c r="S6" t="n">
-        <v>13.4619</v>
+        <v>-1.2773</v>
       </c>
       <c r="T6" t="n">
-        <v>11.2621</v>
+        <v>-0.3214</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2002</v>
+        <v>-0.9559000000000002</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.3165</v>
+        <v>10.3747</v>
       </c>
       <c r="W6" t="n">
-        <v>11.666</v>
+        <v>17.4699</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.9826</v>
+        <v>-7.0952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. GUR</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8955</v>
+        <v>5.929899999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2149</v>
+        <v>11.0038</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1104</v>
+        <v>-5.0743</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.002</v>
+        <v>-25.6569</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1392</v>
+        <v>-19.3575</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1372</v>
+        <v>-6.2995</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.3386</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>-4.5076</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1239</v>
+        <v>4.846399999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07140000000000001</v>
+        <v>-25.9956</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1896</v>
+        <v>-14.8499</v>
       </c>
       <c r="O7" t="n">
-        <v>0.261</v>
+        <v>-11.1459</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>26.6747</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-9.278499999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>35.953</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2623</v>
+        <v>12.229</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1415</v>
+        <v>8.2773</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1208</v>
+        <v>3.9516</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-7.3165</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>11.666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-18.9826</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>L. GUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4027000000000012</v>
+        <v>0.9798</v>
       </c>
       <c r="E8" t="n">
-        <v>28.2655</v>
+        <v>-0.0969</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.8629</v>
+        <v>1.0768</v>
       </c>
       <c r="G8" t="n">
-        <v>-24.3066</v>
+        <v>-0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.1407</v>
+        <v>-0.1392</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.1663</v>
+        <v>0.1372</v>
       </c>
       <c r="J8" t="n">
-        <v>26.9798</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>13.9842</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>12.9953</v>
+        <v>-0.1239</v>
       </c>
       <c r="M8" t="n">
-        <v>-51.2863</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-30.1247</v>
+        <v>-0.1896</v>
       </c>
       <c r="O8" t="n">
-        <v>-21.1618</v>
+        <v>0.261</v>
       </c>
       <c r="P8" t="n">
-        <v>5.567200000000001</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-53.1174</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>58.6841</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>14.7759</v>
+        <v>-0.1779</v>
       </c>
       <c r="T8" t="n">
-        <v>15.7897</v>
+        <v>-0.0235</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0141</v>
+        <v>-0.1544</v>
       </c>
       <c r="V8" t="n">
-        <v>4.3668</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>38.6128</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-34.246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OMORUYI</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8123</v>
+        <v>-0.1658999999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4504</v>
+        <v>4.1069</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2627</v>
+        <v>-4.273000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7901</v>
+        <v>-2.800399999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3552</v>
+        <v>-15.5949</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4349999999999999</v>
+        <v>12.7947</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3246</v>
+        <v>14.1112</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4718</v>
+        <v>-2.5963</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>16.7076</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4655</v>
+        <v>-16.9115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8834</v>
+        <v>-12.9988</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5821999999999999</v>
+        <v>-3.9127</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.4948</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-21.1079</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>27.6025</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9778</v>
+        <v>-3.4971</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8624</v>
+        <v>1.6439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8847</v>
+        <v>-5.141</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3632000000000004</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>9.4595</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>-9.822699999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.858</v>
+        <v>-0.5827</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2497</v>
+        <v>-0.1317</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6083</v>
+        <v>-0.451</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7007</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3892</v>
+        <v>-0.114</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3145</v>
+        <v>-0.1573</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>C. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3504</v>
+        <v>-2.3457</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0111</v>
+        <v>-0.08299999999999996</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.3619</v>
+        <v>-2.2627</v>
       </c>
       <c r="G11" t="n">
-        <v>3.857199999999999</v>
+        <v>-2.7901</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3214</v>
+        <v>-2.3552</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5357</v>
+        <v>-0.4349999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>23.574</v>
+        <v>-1.3246</v>
       </c>
       <c r="K11" t="n">
-        <v>12.9569</v>
+        <v>-1.4718</v>
       </c>
       <c r="L11" t="n">
-        <v>10.617</v>
+        <v>0.1472</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.7171</v>
+        <v>-1.4655</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.6354</v>
+        <v>-0.8834</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.0815</v>
+        <v>-0.5821999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7989</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-33.633</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>27.8344</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-12.7836</v>
+        <v>0.4444</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.399800000000001</v>
+        <v>1.3291</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.3838</v>
+        <v>-0.8847</v>
       </c>
       <c r="V11" t="n">
-        <v>10.3747</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>17.4699</v>
+        <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.0952</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6703</v>
+        <v>-4.6508</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6912000000000003</v>
+        <v>1.1944</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.3614</v>
+        <v>-5.845400000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7336000000000005</v>
@@ -1390,13 +1390,13 @@
         <v>12.0618</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8157</v>
+        <v>3.8353</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1684</v>
+        <v>2.6716</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6474</v>
+        <v>1.1637</v>
       </c>
       <c r="V12" t="n">
         <v>-5.8971</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.0269</v>
+        <v>-7.274899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>18.4681</v>
+        <v>17.8582</v>
       </c>
       <c r="F13" t="n">
-        <v>-31.4952</v>
+        <v>-25.1326</v>
       </c>
       <c r="G13" t="n">
-        <v>-47.0421</v>
+        <v>-24.3066</v>
       </c>
       <c r="H13" t="n">
-        <v>-25.171</v>
+        <v>-16.1407</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.8714</v>
+        <v>-8.1663</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3116</v>
+        <v>26.9798</v>
       </c>
       <c r="K13" t="n">
-        <v>6.1149</v>
+        <v>13.9842</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8037000000000002</v>
+        <v>12.9953</v>
       </c>
       <c r="M13" t="n">
-        <v>-52.3533</v>
+        <v>-51.2863</v>
       </c>
       <c r="N13" t="n">
-        <v>-31.2861</v>
+        <v>-30.1247</v>
       </c>
       <c r="O13" t="n">
-        <v>-21.0679</v>
+        <v>-21.1618</v>
       </c>
       <c r="P13" t="n">
-        <v>25.5151</v>
+        <v>5.567200000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-39.6643</v>
+        <v>-53.1174</v>
       </c>
       <c r="R13" t="n">
-        <v>65.17870000000001</v>
+        <v>58.6841</v>
       </c>
       <c r="S13" t="n">
-        <v>16.7461</v>
+        <v>7.098</v>
       </c>
       <c r="T13" t="n">
-        <v>14.8856</v>
+        <v>5.382000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8605</v>
+        <v>1.716</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.2455</v>
+        <v>4.3668</v>
       </c>
       <c r="W13" t="n">
-        <v>37.935</v>
+        <v>38.6128</v>
       </c>
       <c r="X13" t="n">
-        <v>-46.1805</v>
+        <v>-34.246</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.4929</v>
+        <v>-18.0018</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.7771</v>
+        <v>7.7198</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.7156</v>
+        <v>-25.7215</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.800399999999999</v>
+        <v>-15.7056</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.5949</v>
+        <v>-10.7882</v>
       </c>
       <c r="I14" t="n">
-        <v>12.7947</v>
+        <v>-4.917900000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>14.1112</v>
+        <v>11.3228</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.5963</v>
+        <v>3.0836</v>
       </c>
       <c r="L14" t="n">
-        <v>16.7076</v>
+        <v>8.2392</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.9115</v>
+        <v>-27.0285</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.9988</v>
+        <v>-13.8721</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.9127</v>
+        <v>-13.1568</v>
       </c>
       <c r="P14" t="n">
-        <v>6.4948</v>
+        <v>-3.2475</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.1079</v>
+        <v>-45.231</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6025</v>
+        <v>41.9839</v>
       </c>
       <c r="S14" t="n">
-        <v>-16.8237</v>
+        <v>0.3356</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.240500000000001</v>
+        <v>5.5537</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.583400000000001</v>
+        <v>-5.2178</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3632000000000004</v>
+        <v>0.6158000000000006</v>
       </c>
       <c r="W14" t="n">
-        <v>9.4595</v>
+        <v>36.0742</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.822699999999999</v>
+        <v>-35.4584</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>-23.8132</v>
+        <v>-22.1125</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9115</v>
+        <v>-6.759000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-29.725</v>
+        <v>-15.3534</v>
       </c>
       <c r="G15" t="n">
-        <v>-15.7056</v>
+        <v>-18.2284</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.7882</v>
+        <v>-21.3026</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.917900000000001</v>
+        <v>3.0743</v>
       </c>
       <c r="J15" t="n">
-        <v>11.3228</v>
+        <v>14.8077</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0836</v>
+        <v>0.7119000000000004</v>
       </c>
       <c r="L15" t="n">
-        <v>8.2392</v>
+        <v>14.0958</v>
       </c>
       <c r="M15" t="n">
-        <v>-27.0285</v>
+        <v>-33.0362</v>
       </c>
       <c r="N15" t="n">
-        <v>-13.8721</v>
+        <v>-22.0149</v>
       </c>
       <c r="O15" t="n">
-        <v>-13.1568</v>
+        <v>-11.021</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2475</v>
+        <v>-13.6852</v>
       </c>
       <c r="Q15" t="n">
-        <v>-45.231</v>
+        <v>-54.9729</v>
       </c>
       <c r="R15" t="n">
-        <v>41.9839</v>
+        <v>41.2878</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.4763</v>
+        <v>-9.370699999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>3.745499999999999</v>
+        <v>-6.3725</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.2212</v>
+        <v>-2.9979</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6158000000000006</v>
+        <v>19.1715</v>
       </c>
       <c r="W15" t="n">
-        <v>36.0742</v>
+        <v>39.7783</v>
       </c>
       <c r="X15" t="n">
-        <v>-35.4584</v>
+        <v>-20.6069</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>-38.7012</v>
+        <v>-26.1854</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.5304</v>
+        <v>7.588500000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.1707</v>
+        <v>-33.7742</v>
       </c>
       <c r="G16" t="n">
-        <v>-18.2284</v>
+        <v>-47.0421</v>
       </c>
       <c r="H16" t="n">
-        <v>-21.3026</v>
+        <v>-25.171</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0743</v>
+        <v>-21.8714</v>
       </c>
       <c r="J16" t="n">
-        <v>14.8077</v>
+        <v>5.3116</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7119000000000004</v>
+        <v>6.1149</v>
       </c>
       <c r="L16" t="n">
-        <v>14.0958</v>
+        <v>-0.8037000000000002</v>
       </c>
       <c r="M16" t="n">
-        <v>-33.0362</v>
+        <v>-52.3533</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.0149</v>
+        <v>-31.2861</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.021</v>
+        <v>-21.0679</v>
       </c>
       <c r="P16" t="n">
-        <v>-13.6852</v>
+        <v>25.5151</v>
       </c>
       <c r="Q16" t="n">
-        <v>-54.9729</v>
+        <v>-39.6643</v>
       </c>
       <c r="R16" t="n">
-        <v>41.2878</v>
+        <v>65.17870000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-25.9591</v>
+        <v>3.587999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-21.1436</v>
+        <v>4.006600000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.8152</v>
+        <v>-0.4185</v>
       </c>
       <c r="V16" t="n">
-        <v>19.1715</v>
+        <v>-8.2455</v>
       </c>
       <c r="W16" t="n">
-        <v>39.7783</v>
+        <v>37.935</v>
       </c>
       <c r="X16" t="n">
-        <v>-20.6069</v>
+        <v>-46.1805</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>-53.5835</v>
+        <v>-31.3613</v>
       </c>
       <c r="E17" t="n">
-        <v>-47.7364</v>
+        <v>-31.8172</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.847</v>
+        <v>0.4557999999999998</v>
       </c>
       <c r="G17" t="n">
         <v>23.8918</v>
@@ -1780,13 +1780,13 @@
         <v>46.8548</v>
       </c>
       <c r="S17" t="n">
-        <v>-28.9647</v>
+        <v>-6.742699999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-18.7485</v>
+        <v>-2.8292</v>
       </c>
       <c r="U17" t="n">
-        <v>-10.2161</v>
+        <v>-3.9129</v>
       </c>
       <c r="V17" t="n">
         <v>5.5339</v>
@@ -1813,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>-72.73310000000001</v>
+        <v>-54.2114</v>
       </c>
       <c r="E18" t="n">
-        <v>-37.2911</v>
+        <v>-24.6669</v>
       </c>
       <c r="F18" t="n">
-        <v>-35.4418</v>
+        <v>-29.5446</v>
       </c>
       <c r="G18" t="n">
         <v>-2.439100000000002</v>
@@ -1858,13 +1858,13 @@
         <v>57.2924</v>
       </c>
       <c r="S18" t="n">
-        <v>-21.4568</v>
+        <v>-2.9357</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.3057</v>
+        <v>1.3184</v>
       </c>
       <c r="U18" t="n">
-        <v>-10.1513</v>
+        <v>-4.2538</v>
       </c>
       <c r="V18" t="n">
         <v>-17.0597</v>
@@ -1891,13 +1891,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>-96.64580000000001</v>
+        <v>-62.6401</v>
       </c>
       <c r="E19" t="n">
-        <v>82.0702</v>
+        <v>93.27169999999998</v>
       </c>
       <c r="F19" t="n">
-        <v>-178.7166</v>
+        <v>-155.9121</v>
       </c>
       <c r="G19" t="n">
         <v>-134.97</v>
@@ -1906,7 +1906,7 @@
         <v>-128.0795</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.8918</v>
+        <v>-6.891800000000005</v>
       </c>
       <c r="J19" t="n">
         <v>283.7245</v>
@@ -1927,7 +1927,7 @@
         <v>-159.6919</v>
       </c>
       <c r="P19" t="n">
-        <v>23.19620000000001</v>
+        <v>23.19619999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-540.452</v>
@@ -1936,16 +1936,16 @@
         <v>563.6476</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3861000000000061</v>
+        <v>33.6187</v>
       </c>
       <c r="T19" t="n">
-        <v>38.455</v>
+        <v>49.6566</v>
       </c>
       <c r="U19" t="n">
-        <v>-38.84</v>
+        <v>-16.0363</v>
       </c>
       <c r="V19" t="n">
-        <v>15.51599999999999</v>
+        <v>15.516</v>
       </c>
       <c r="W19" t="n">
         <v>300.3389</v>
